--- a/testData/testPlanTabTestData/testPlanTab_TestData.xlsx
+++ b/testData/testPlanTabTestData/testPlanTab_TestData.xlsx
@@ -1,11 +1,10 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29825"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
+  <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{50A17C1B-E87E-48F1-AAD8-77DA9C49EEFA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="240" yWindow="105" windowWidth="14805" windowHeight="8010" firstSheet="64" activeTab="64" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView windowWidth="19200" windowHeight="6800" firstSheet="61" activeTab="70"/>
   </bookViews>
   <sheets>
     <sheet name="tc002" sheetId="2" r:id="rId1"/>
@@ -76,12 +75,12 @@
     <sheet name="tc076" sheetId="56" r:id="rId66"/>
     <sheet name="tc077" sheetId="57" r:id="rId67"/>
     <sheet name="tc078" sheetId="58" r:id="rId68"/>
+    <sheet name="tc088" sheetId="71" r:id="rId69"/>
+    <sheet name="tc089" sheetId="72" r:id="rId70"/>
+    <sheet name="tc090" sheetId="73" r:id="rId71"/>
   </sheets>
-  <calcPr calcId="191028"/>
+  <calcPr calcId="191029"/>
   <extLst>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
-      <x15:workbookPr chartTrackingRefBase="1"/>
-    </ext>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
       <xcalcf:calcFeatures>
         <xcalcf:feature name="microsoft.com:RD"/>
@@ -98,7 +97,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="442" uniqueCount="82">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="458" uniqueCount="83">
   <si>
     <t>projectName</t>
   </si>
@@ -345,28 +344,28 @@
   <si>
     <t xml:space="preserve">Release testing </t>
   </si>
+  <si>
+    <t>Cycle</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="8">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="xr9">
+  <numFmts count="5">
+    <numFmt numFmtId="176" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="177" formatCode="_ &quot;₹&quot;* #,##0.00_ ;_ &quot;₹&quot;* \-#,##0.00_ ;_ &quot;₹&quot;* &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="178" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
+    <numFmt numFmtId="179" formatCode="_ &quot;₹&quot;* #,##0_ ;_ &quot;₹&quot;* \-#,##0_ ;_ &quot;₹&quot;* &quot;-&quot;_ ;_ @_ "/>
+    <numFmt numFmtId="180" formatCode="dd/mm/yyyy"/>
+  </numFmts>
+  <fonts count="25">
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Aptos Narrow"/>
-      <family val="2"/>
+      <charset val="134"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF000000"/>
-      <name val="Aptos Narrow"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
     </font>
     <font>
       <sz val="11"/>
@@ -376,39 +375,367 @@
     </font>
     <font>
       <sz val="11"/>
+      <color rgb="FF000000"/>
+      <name val="Aptos Narrow"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="9.8"/>
+      <color rgb="FFBCBEC4"/>
+      <name val="JetBrains Mono"/>
+      <charset val="1"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Aptos Narrow"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
       <name val="Calibri"/>
-      <family val="2"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF0000FF"/>
+      <name val="Aptos Narrow"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF800080"/>
+      <name val="Aptos Narrow"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="Aptos Narrow"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="18"/>
+      <color theme="3"/>
+      <name val="Aptos Narrow"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF7F7F7F"/>
+      <name val="Aptos Narrow"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="15"/>
+      <color theme="3"/>
+      <name val="Aptos Narrow"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="13"/>
+      <color theme="3"/>
+      <name val="Aptos Narrow"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="3"/>
+      <name val="Aptos Narrow"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF3F3F76"/>
+      <name val="Aptos Narrow"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF3F3F3F"/>
+      <name val="Aptos Narrow"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="Aptos Narrow"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="Aptos Narrow"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="Aptos Narrow"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Aptos Narrow"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
+      <name val="Aptos Narrow"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
+      <name val="Aptos Narrow"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C6500"/>
+      <name val="Aptos Narrow"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="Aptos Narrow"/>
+      <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="Calibri"/>
-      <family val="2"/>
+      <name val="Aptos Narrow"/>
+      <charset val="0"/>
       <scheme val="minor"/>
     </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF000000"/>
-      <name val="Aptos Narrow"/>
-    </font>
-    <font>
-      <sz val="9.8000000000000007"/>
-      <color rgb="FFBCBEC4"/>
-      <name val="JetBrains Mono"/>
-      <family val="3"/>
-      <charset val="1"/>
-    </font>
   </fonts>
-  <fills count="2">
+  <fills count="33">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="1">
+  <borders count="9">
     <border>
       <left/>
       <right/>
@@ -416,33 +743,318 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFB2B2B2"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFB2B2B2"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFB2B2B2"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFB2B2B2"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF7F7F7F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF7F7F7F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF7F7F7F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF7F7F7F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="double">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="double">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="double">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="double">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color theme="4"/>
+      </top>
+      <bottom style="double">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="179" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="3" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="14" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="180" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="180" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="49">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="Comma" xfId="1" builtinId="3"/>
+    <cellStyle name="Currency" xfId="2" builtinId="4"/>
+    <cellStyle name="Percent" xfId="3" builtinId="5"/>
+    <cellStyle name="Comma [0]" xfId="4" builtinId="6"/>
+    <cellStyle name="Currency [0]" xfId="5" builtinId="7"/>
+    <cellStyle name="Link" xfId="6" builtinId="8"/>
+    <cellStyle name="Followed Hyperlink" xfId="7" builtinId="9"/>
+    <cellStyle name="Note" xfId="8" builtinId="10"/>
+    <cellStyle name="Warning Text" xfId="9" builtinId="11"/>
+    <cellStyle name="Title" xfId="10" builtinId="15"/>
+    <cellStyle name="CExplanatory Text" xfId="11" builtinId="53"/>
+    <cellStyle name="Heading 1" xfId="12" builtinId="16"/>
+    <cellStyle name="Heading 2" xfId="13" builtinId="17"/>
+    <cellStyle name="Heading 3" xfId="14" builtinId="18"/>
+    <cellStyle name="Heading 4" xfId="15" builtinId="19"/>
+    <cellStyle name="Input" xfId="16" builtinId="20"/>
+    <cellStyle name="Output" xfId="17" builtinId="21"/>
+    <cellStyle name="Calculation" xfId="18" builtinId="22"/>
+    <cellStyle name="Check Cell" xfId="19" builtinId="23"/>
+    <cellStyle name="Linked Cell" xfId="20" builtinId="24"/>
+    <cellStyle name="Total" xfId="21" builtinId="25"/>
+    <cellStyle name="Good" xfId="22" builtinId="26"/>
+    <cellStyle name="Bad" xfId="23" builtinId="27"/>
+    <cellStyle name="Neutral" xfId="24" builtinId="28"/>
+    <cellStyle name="Accent1" xfId="25" builtinId="29"/>
+    <cellStyle name="20% - Accent1" xfId="26" builtinId="30"/>
+    <cellStyle name="40% - Accent1" xfId="27" builtinId="31"/>
+    <cellStyle name="60% - Accent1" xfId="28" builtinId="32"/>
+    <cellStyle name="Accent2" xfId="29" builtinId="33"/>
+    <cellStyle name="20% - Accent2" xfId="30" builtinId="34"/>
+    <cellStyle name="40% - Accent2" xfId="31" builtinId="35"/>
+    <cellStyle name="60% - Accent2" xfId="32" builtinId="36"/>
+    <cellStyle name="Accent3" xfId="33" builtinId="37"/>
+    <cellStyle name="20% - Accent3" xfId="34" builtinId="38"/>
+    <cellStyle name="40% - Accent3" xfId="35" builtinId="39"/>
+    <cellStyle name="60% - Accent3" xfId="36" builtinId="40"/>
+    <cellStyle name="Accent4" xfId="37" builtinId="41"/>
+    <cellStyle name="20% - Accent4" xfId="38" builtinId="42"/>
+    <cellStyle name="40% - Accent4" xfId="39" builtinId="43"/>
+    <cellStyle name="60% - Accent4" xfId="40" builtinId="44"/>
+    <cellStyle name="Accent5" xfId="41" builtinId="45"/>
+    <cellStyle name="20% - Accent5" xfId="42" builtinId="46"/>
+    <cellStyle name="40% - Accent5" xfId="43" builtinId="47"/>
+    <cellStyle name="60% - Accent5" xfId="44" builtinId="48"/>
+    <cellStyle name="Accent6" xfId="45" builtinId="49"/>
+    <cellStyle name="20% - Accent6" xfId="46" builtinId="50"/>
+    <cellStyle name="40% - Accent6" xfId="47" builtinId="51"/>
+    <cellStyle name="60% - Accent6" xfId="48" builtinId="52"/>
   </cellStyles>
-  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleMedium9"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
     </ext>
   </extLst>
 </styleSheet>
@@ -491,7 +1103,7 @@
     </a:clrScheme>
     <a:fontScheme name="Office">
       <a:majorFont>
-        <a:latin typeface="Aptos Display" panose="020F0302020204030204"/>
+        <a:latin typeface="Aptos Display"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="游ゴシック Light"/>
@@ -524,26 +1136,9 @@
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
         <a:font script="Geor" typeface="Sylfaen"/>
-        <a:font script="Armn" typeface="Arial"/>
-        <a:font script="Bugi" typeface="Leelawadee UI"/>
-        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
-        <a:font script="Java" typeface="Javanese Text"/>
-        <a:font script="Lisu" typeface="Segoe UI"/>
-        <a:font script="Mymr" typeface="Myanmar Text"/>
-        <a:font script="Nkoo" typeface="Ebrima"/>
-        <a:font script="Olck" typeface="Nirmala UI"/>
-        <a:font script="Osma" typeface="Ebrima"/>
-        <a:font script="Phag" typeface="Phagspa"/>
-        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
-        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
-        <a:font script="Syre" typeface="Estrangelo Edessa"/>
-        <a:font script="Sora" typeface="Nirmala UI"/>
-        <a:font script="Tale" typeface="Microsoft Tai Le"/>
-        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
-        <a:font script="Tfng" typeface="Ebrima"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Aptos Narrow" panose="02110004020202020204"/>
+        <a:latin typeface="Aptos Narrow"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="游ゴシック"/>
@@ -576,23 +1171,6 @@
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
         <a:font script="Geor" typeface="Sylfaen"/>
-        <a:font script="Armn" typeface="Arial"/>
-        <a:font script="Bugi" typeface="Leelawadee UI"/>
-        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
-        <a:font script="Java" typeface="Javanese Text"/>
-        <a:font script="Lisu" typeface="Segoe UI"/>
-        <a:font script="Mymr" typeface="Myanmar Text"/>
-        <a:font script="Nkoo" typeface="Ebrima"/>
-        <a:font script="Olck" typeface="Nirmala UI"/>
-        <a:font script="Osma" typeface="Ebrima"/>
-        <a:font script="Phag" typeface="Phagspa"/>
-        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
-        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
-        <a:font script="Syre" typeface="Estrangelo Edessa"/>
-        <a:font script="Sora" typeface="Nirmala UI"/>
-        <a:font script="Tale" typeface="Microsoft Tai Le"/>
-        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
-        <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
     <a:fmtScheme name="Office">
@@ -754,22 +1332,17 @@
       </a:style>
     </a:lnDef>
   </a:objectDefaults>
-  <a:extraClrSchemeLst/>
-  <a:extLst>
-    <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
-    </a:ext>
-  </a:extLst>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2B23743E-2A7E-44B5-B321-E0E01B81F69B}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
   <dimension ref="A1:B2"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" outlineLevelRow="1" outlineLevelCol="1"/>
   <cols>
-    <col min="1" max="1" width="35.5703125" customWidth="1"/>
-    <col min="2" max="2" width="25.28515625" customWidth="1"/>
+    <col min="1" max="1" width="35.575" customWidth="1"/>
+    <col min="2" max="2" width="25.2833333333333" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:2">
@@ -781,111 +1354,203 @@
       </c>
     </row>
     <row r="2" spans="1:2">
+      <c r="A2" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="B2" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <headerFooter/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
+  <dimension ref="A1:D2"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" outlineLevelRow="1" outlineLevelCol="3"/>
+  <cols>
+    <col min="1" max="1" width="33.425" customWidth="1"/>
+    <col min="2" max="2" width="23.425" customWidth="1"/>
+    <col min="3" max="3" width="21.2833333333333" customWidth="1"/>
+    <col min="4" max="4" width="24.2833333333333" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:4">
+      <c r="A1" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4">
       <c r="A2" s="1" t="s">
         <v>2</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>3</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{411C2460-46F2-4D6D-BFEF-84764CCAC17E}">
+        <v>25</v>
+      </c>
+      <c r="C2" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="D2" s="1" t="s">
+        <v>27</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <headerFooter/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
   <dimension ref="A1:D2"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultColWidth="17.7083333333333" defaultRowHeight="14" outlineLevelRow="1" outlineLevelCol="3"/>
+  <sheetData>
+    <row r="1" spans="1:4">
+      <c r="A1" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4">
+      <c r="A2" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="C2" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="D2" s="1" t="s">
+        <v>27</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <headerFooter/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
+  <dimension ref="A1:C2"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" outlineLevelRow="1" outlineLevelCol="2"/>
   <cols>
-    <col min="1" max="1" width="33.42578125" customWidth="1"/>
-    <col min="2" max="2" width="23.42578125" customWidth="1"/>
-    <col min="3" max="3" width="21.28515625" customWidth="1"/>
-    <col min="4" max="4" width="24.28515625" customWidth="1"/>
+    <col min="1" max="1" width="32.575" customWidth="1"/>
+    <col min="2" max="2" width="22.1333333333333" customWidth="1"/>
+    <col min="3" max="3" width="23.425" customWidth="1"/>
   </cols>
   <sheetData>
+    <row r="1" ht="14.5" spans="1:3">
+      <c r="A1" s="8" t="s">
+        <v>9</v>
+      </c>
+      <c r="B1" s="8" t="s">
+        <v>10</v>
+      </c>
+      <c r="C1" s="8" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="2" ht="14.5" spans="1:3">
+      <c r="A2" s="8" t="s">
+        <v>2</v>
+      </c>
+      <c r="B2" s="8" t="s">
+        <v>28</v>
+      </c>
+      <c r="C2" s="8" t="s">
+        <v>29</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <headerFooter/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
+  <dimension ref="A1:D2"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" outlineLevelRow="1" outlineLevelCol="3"/>
+  <cols>
+    <col min="1" max="1" width="32.7083333333333" customWidth="1"/>
+    <col min="2" max="2" width="19.575" customWidth="1"/>
+    <col min="3" max="3" width="13.2833333333333" customWidth="1"/>
+    <col min="4" max="4" width="27.2833333333333" customWidth="1"/>
+  </cols>
+  <sheetData>
     <row r="1" spans="1:4">
-      <c r="A1" s="4" t="s">
-        <v>9</v>
-      </c>
-      <c r="B1" s="4" t="s">
-        <v>22</v>
-      </c>
-      <c r="C1" s="4" t="s">
-        <v>23</v>
-      </c>
-      <c r="D1" s="4" t="s">
-        <v>24</v>
+      <c r="A1" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B1" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="C1" s="7" t="s">
+        <v>30</v>
+      </c>
+      <c r="D1" s="7" t="s">
+        <v>31</v>
       </c>
     </row>
     <row r="2" spans="1:4">
-      <c r="A2" s="4" t="s">
-        <v>2</v>
-      </c>
-      <c r="B2" s="4" t="s">
-        <v>25</v>
-      </c>
-      <c r="C2" s="4" t="s">
-        <v>26</v>
-      </c>
-      <c r="D2" s="4" t="s">
-        <v>27</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FA8D4F1F-91FD-4EAB-B2C3-E35DD4FBCE03}">
+      <c r="A2" s="6" t="s">
+        <v>2</v>
+      </c>
+      <c r="B2" s="7" t="s">
+        <v>32</v>
+      </c>
+      <c r="C2" s="7" t="s">
+        <v>33</v>
+      </c>
+      <c r="D2" s="7" t="s">
+        <v>34</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <headerFooter/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
   <dimension ref="A1:D2"/>
-  <sheetFormatPr defaultColWidth="17.7109375" defaultRowHeight="15"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" outlineLevelRow="1" outlineLevelCol="3"/>
+  <cols>
+    <col min="1" max="1" width="14.1333333333333" customWidth="1"/>
+    <col min="2" max="2" width="15" customWidth="1"/>
+    <col min="3" max="3" width="18" customWidth="1"/>
+    <col min="4" max="4" width="16.2833333333333" customWidth="1"/>
+  </cols>
   <sheetData>
     <row r="1" spans="1:4">
-      <c r="A1" s="4" t="s">
-        <v>9</v>
-      </c>
-      <c r="B1" s="4" t="s">
-        <v>22</v>
-      </c>
-      <c r="C1" s="4" t="s">
-        <v>23</v>
-      </c>
-      <c r="D1" s="4" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="2" spans="1:4">
-      <c r="A2" s="4" t="s">
-        <v>2</v>
-      </c>
-      <c r="B2" s="4" t="s">
-        <v>25</v>
-      </c>
-      <c r="C2" s="4" t="s">
-        <v>26</v>
-      </c>
-      <c r="D2" s="4" t="s">
-        <v>27</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{629D3112-3371-4BF7-8E34-7EF404484B7A}">
-  <dimension ref="A1:C2"/>
-  <sheetFormatPr defaultRowHeight="15"/>
-  <cols>
-    <col min="1" max="1" width="32.5703125" customWidth="1"/>
-    <col min="2" max="2" width="22.140625" customWidth="1"/>
-    <col min="3" max="3" width="23.42578125" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:3">
       <c r="A1" s="2" t="s">
         <v>9</v>
       </c>
@@ -895,13 +1560,508 @@
       <c r="C1" s="2" t="s">
         <v>11</v>
       </c>
+      <c r="D1" s="2" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4">
+      <c r="A2" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="B2" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="C2" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="D2" s="2" t="s">
+        <v>37</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <headerFooter/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
+  <dimension ref="A1:H2"/>
+  <sheetFormatPr defaultColWidth="18" defaultRowHeight="14" outlineLevelRow="1" outlineLevelCol="7"/>
+  <sheetData>
+    <row r="1" spans="1:8">
+      <c r="A1" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="B1" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="C1" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="D1" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="E1" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="F1" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="G1" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="H1" s="2" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="2" spans="1:8">
+      <c r="A2" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="B2" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="C2" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="D2" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="E2" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="F2" s="3">
+        <v>45944</v>
+      </c>
+      <c r="G2" s="3">
+        <v>45955</v>
+      </c>
+      <c r="H2" s="2" t="s">
+        <v>21</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <headerFooter/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
+  <dimension ref="A1:A2"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" outlineLevelRow="1"/>
+  <sheetData>
+    <row r="1" spans="1:1">
+      <c r="A1" s="2" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2" spans="1:1">
+      <c r="A2" s="2" t="s">
+        <v>2</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <headerFooter/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
+  <dimension ref="A1:B2"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" outlineLevelRow="1" outlineLevelCol="1"/>
+  <cols>
+    <col min="1" max="1" width="29.2833333333333" customWidth="1"/>
+    <col min="2" max="2" width="21.2833333333333" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:2">
+      <c r="A1" t="s">
+        <v>9</v>
+      </c>
+      <c r="B1" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2">
+      <c r="A2" t="s">
+        <v>2</v>
+      </c>
+      <c r="B2" t="s">
+        <v>32</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <headerFooter/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
+  <dimension ref="A1:B2"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" outlineLevelRow="1" outlineLevelCol="1"/>
+  <cols>
+    <col min="1" max="1" width="29.575" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:2">
+      <c r="A1" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2">
+      <c r="A2" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>38</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <headerFooter/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
+  <dimension ref="A1:B2"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" outlineLevelRow="1" outlineLevelCol="1"/>
+  <sheetData>
+    <row r="1" spans="1:2">
+      <c r="A1" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2">
+      <c r="A2" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="B2" s="2" t="s">
+        <v>8</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <headerFooter/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
+  <dimension ref="A1:A2"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" outlineLevelRow="1"/>
+  <sheetData>
+    <row r="1" spans="1:1">
+      <c r="A1" s="2" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2" spans="1:1">
+      <c r="A2" s="2" t="s">
+        <v>2</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <headerFooter/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet20.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
+  <dimension ref="A1:D2"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" outlineLevelRow="1" outlineLevelCol="3"/>
+  <cols>
+    <col min="1" max="1" width="16" customWidth="1"/>
+    <col min="2" max="2" width="19.575" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:4">
+      <c r="A1" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="B1" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="C1" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="D1" s="2" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4">
+      <c r="A2" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="B2" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="C2" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="D2" s="2" t="s">
+        <v>15</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <headerFooter/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet21.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
+  <dimension ref="A1:H2"/>
+  <sheetFormatPr defaultColWidth="17.575" defaultRowHeight="14" outlineLevelRow="1" outlineLevelCol="7"/>
+  <sheetData>
+    <row r="1" spans="1:8">
+      <c r="A1" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="B1" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="C1" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="D1" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="E1" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="F1" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="G1" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="H1" s="2" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="2" spans="1:8">
+      <c r="A2" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="B2" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="C2" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="D2" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="E2" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="F2" s="3">
+        <v>45944</v>
+      </c>
+      <c r="G2" s="3">
+        <v>45955</v>
+      </c>
+      <c r="H2" s="2" t="s">
+        <v>21</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <headerFooter/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet22.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
+  <dimension ref="A1:C2"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" outlineLevelRow="1" outlineLevelCol="2"/>
+  <sheetData>
+    <row r="1" spans="1:3">
+      <c r="A1" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="B1" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="C1" t="s">
+        <v>39</v>
+      </c>
     </row>
     <row r="2" spans="1:3">
       <c r="A2" s="2" t="s">
         <v>2</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>28</v>
+        <v>13</v>
+      </c>
+      <c r="C2" t="s">
+        <v>40</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <headerFooter/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet23.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
+  <dimension ref="A1:D2"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" outlineLevelRow="1" outlineLevelCol="3"/>
+  <sheetData>
+    <row r="1" spans="1:4">
+      <c r="A1" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="B1" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="C1" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="D1" s="2" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4">
+      <c r="A2" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="B2" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="C2" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="D2" s="2" t="s">
+        <v>15</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <headerFooter/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet24.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
+  <dimension ref="A1:E2"/>
+  <sheetFormatPr defaultColWidth="18.2833333333333" defaultRowHeight="14" outlineLevelRow="1" outlineLevelCol="4"/>
+  <sheetData>
+    <row r="1" spans="1:5">
+      <c r="A1" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="E1" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5">
+      <c r="A2" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="C2" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="D2" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="E2" t="s">
+        <v>41</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <headerFooter/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet25.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
+  <dimension ref="A1:B2"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" outlineLevelRow="1" outlineLevelCol="1"/>
+  <sheetData>
+    <row r="1" spans="1:2">
+      <c r="A1" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="B1" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2">
+      <c r="A2" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="B2" s="2" t="s">
+        <v>43</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <headerFooter/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet26.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
+  <dimension ref="A1:C2"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" outlineLevelRow="1" outlineLevelCol="2"/>
+  <sheetData>
+    <row r="1" spans="1:3">
+      <c r="A1" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="B1" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="C1" s="2" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3">
+      <c r="A2" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="B2" s="2" t="s">
+        <v>44</v>
       </c>
       <c r="C2" s="2" t="s">
         <v>29</v>
@@ -909,602 +2069,55 @@
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AB833951-6912-4EC9-ACE3-69E572816D68}">
+  <headerFooter/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet27.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
   <dimension ref="A1:D2"/>
-  <sheetFormatPr defaultRowHeight="15"/>
-  <cols>
-    <col min="1" max="1" width="32.7109375" customWidth="1"/>
-    <col min="2" max="2" width="19.5703125" customWidth="1"/>
-    <col min="3" max="3" width="13.28515625" customWidth="1"/>
-    <col min="4" max="4" width="27.28515625" customWidth="1"/>
-  </cols>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" outlineLevelRow="1" outlineLevelCol="3"/>
   <sheetData>
     <row r="1" spans="1:4">
-      <c r="A1" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="B1" s="6" t="s">
+      <c r="A1" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="B1" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="C1" s="6" t="s">
-        <v>30</v>
-      </c>
-      <c r="D1" s="6" t="s">
-        <v>31</v>
+      <c r="C1" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="D1" s="2" t="s">
+        <v>24</v>
       </c>
     </row>
     <row r="2" spans="1:4">
-      <c r="A2" s="5" t="s">
-        <v>2</v>
-      </c>
-      <c r="B2" s="6" t="s">
-        <v>32</v>
-      </c>
-      <c r="C2" s="6" t="s">
-        <v>33</v>
-      </c>
-      <c r="D2" s="6" t="s">
-        <v>34</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0525B04B-FF17-434F-88AB-61B4785D0097}">
-  <dimension ref="A1:D2"/>
-  <sheetFormatPr defaultRowHeight="15"/>
-  <cols>
-    <col min="1" max="1" width="14.140625" customWidth="1"/>
-    <col min="2" max="2" width="15" customWidth="1"/>
-    <col min="3" max="3" width="18" customWidth="1"/>
-    <col min="4" max="4" width="16.28515625" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:4">
-      <c r="A1" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="2" spans="1:4">
-      <c r="A2" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="B2" s="1" t="s">
-        <v>35</v>
-      </c>
-      <c r="C2" s="1" t="s">
-        <v>36</v>
-      </c>
-      <c r="D2" s="1" t="s">
-        <v>37</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1C4751AE-761A-4E86-AB60-FFA9CFAB4E24}">
-  <dimension ref="A1:H2"/>
-  <sheetFormatPr defaultColWidth="18" defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1" spans="1:8">
-      <c r="A1" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="F1" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="G1" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="H1" s="1" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="2" spans="1:8">
-      <c r="A2" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="B2" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="C2" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="D2" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="E2" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="F2" s="3">
-        <v>45944</v>
-      </c>
-      <c r="G2" s="3">
-        <v>45955</v>
-      </c>
-      <c r="H2" s="1" t="s">
-        <v>21</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E586B257-6C9A-4EFD-A8EB-37EC5826DD12}">
+      <c r="A2" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="B2" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="C2" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="D2" s="2" t="s">
+        <v>46</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <headerFooter/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet28.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
   <dimension ref="A1:A2"/>
-  <sheetFormatPr defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1" spans="1:1">
-      <c r="A1" s="1" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="2" spans="1:1">
-      <c r="A2" s="1" t="s">
-        <v>2</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0EAB45CC-E342-4AFE-8447-7AB01267C45A}">
-  <dimension ref="A1:B2"/>
-  <sheetFormatPr defaultRowHeight="15"/>
-  <cols>
-    <col min="1" max="1" width="29.28515625" customWidth="1"/>
-    <col min="2" max="2" width="21.28515625" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:2">
-      <c r="A1" t="s">
-        <v>9</v>
-      </c>
-      <c r="B1" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="2" spans="1:2">
-      <c r="A2" t="s">
-        <v>2</v>
-      </c>
-      <c r="B2" t="s">
-        <v>32</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3DE43DAC-405D-4ECE-ABBB-9AED0190BE69}">
-  <dimension ref="A1:B2"/>
-  <sheetFormatPr defaultRowHeight="15"/>
-  <cols>
-    <col min="1" max="1" width="29.5703125" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:2">
-      <c r="A1" s="4" t="s">
-        <v>9</v>
-      </c>
-      <c r="B1" s="4" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="2" spans="1:2">
-      <c r="A2" s="4" t="s">
-        <v>2</v>
-      </c>
-      <c r="B2" s="4" t="s">
-        <v>38</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0CCC4F11-6D57-4E86-BC2C-B96433CE4912}">
-  <dimension ref="A1:B2"/>
-  <sheetFormatPr defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1" spans="1:2">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="2" spans="1:2">
-      <c r="A2" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="B2" s="1" t="s">
-        <v>8</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F436E5F8-B3BC-468E-8E9A-70F569ADF0EB}">
-  <dimension ref="A1:A2"/>
-  <sheetFormatPr defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1" spans="1:1">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="2" spans="1:1">
-      <c r="A2" s="1" t="s">
-        <v>2</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet20.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8DEC3E30-F85F-457B-9409-1C89CD251738}">
-  <dimension ref="A1:D2"/>
-  <sheetFormatPr defaultRowHeight="15"/>
-  <cols>
-    <col min="1" max="1" width="16" customWidth="1"/>
-    <col min="2" max="2" width="19.5703125" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:4">
-      <c r="A1" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="2" spans="1:4">
-      <c r="A2" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="B2" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="C2" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="D2" s="1" t="s">
-        <v>15</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet21.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EDBD1B0F-19E9-4391-A5F0-2D34BAEAAD84}">
-  <dimension ref="A1:H2"/>
-  <sheetFormatPr defaultColWidth="17.5703125" defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1" spans="1:8">
-      <c r="A1" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="F1" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="G1" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="H1" s="1" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="2" spans="1:8">
-      <c r="A2" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="B2" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="C2" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="D2" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="E2" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="F2" s="3">
-        <v>45944</v>
-      </c>
-      <c r="G2" s="3">
-        <v>45955</v>
-      </c>
-      <c r="H2" s="1" t="s">
-        <v>21</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet22.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E3940326-2450-4816-877F-936C99DD45DE}">
-  <dimension ref="A1:C2"/>
-  <sheetFormatPr defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1" spans="1:3">
-      <c r="A1" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="C1" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="2" spans="1:3">
-      <c r="A2" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="B2" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="C2" t="s">
-        <v>40</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet23.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{59FDD84E-D2EC-4707-9E15-C69F2652F8A4}">
-  <dimension ref="A1:D2"/>
-  <sheetFormatPr defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1" spans="1:4">
-      <c r="A1" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="2" spans="1:4">
-      <c r="A2" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="B2" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="C2" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="D2" s="1" t="s">
-        <v>15</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet24.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8847E28B-B819-49CB-8996-659E48CE0A8B}">
-  <dimension ref="A1:E2"/>
-  <sheetFormatPr defaultColWidth="18.28515625" defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1" spans="1:5">
-      <c r="A1" s="4" t="s">
-        <v>9</v>
-      </c>
-      <c r="B1" s="4" t="s">
-        <v>22</v>
-      </c>
-      <c r="C1" s="4" t="s">
-        <v>23</v>
-      </c>
-      <c r="D1" s="4" t="s">
-        <v>24</v>
-      </c>
-      <c r="E1" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="2" spans="1:5">
-      <c r="A2" s="4" t="s">
-        <v>2</v>
-      </c>
-      <c r="B2" s="4" t="s">
-        <v>25</v>
-      </c>
-      <c r="C2" s="4" t="s">
-        <v>26</v>
-      </c>
-      <c r="D2" s="4" t="s">
-        <v>27</v>
-      </c>
-      <c r="E2" t="s">
-        <v>41</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet25.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EA990625-794E-40F2-9AFD-E8166BB37172}">
-  <dimension ref="A1:B2"/>
-  <sheetFormatPr defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1" spans="1:2">
-      <c r="A1" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="2" spans="1:2">
-      <c r="A2" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="B2" s="1" t="s">
-        <v>43</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet26.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7DBFBAB1-399B-46B6-8F99-3EED558ABBED}">
-  <dimension ref="A1:C2"/>
-  <sheetFormatPr defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1" spans="1:3">
-      <c r="A1" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="2" spans="1:3">
-      <c r="A2" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="B2" s="1" t="s">
-        <v>44</v>
-      </c>
-      <c r="C2" s="1" t="s">
-        <v>29</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet27.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B7402964-2142-40F0-844C-0525DEED8BED}">
-  <dimension ref="A1:D2"/>
-  <sheetFormatPr defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1" spans="1:4">
-      <c r="A1" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="2" spans="1:4">
-      <c r="A2" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="B2" s="1" t="s">
-        <v>44</v>
-      </c>
-      <c r="C2" s="1" t="s">
-        <v>45</v>
-      </c>
-      <c r="D2" s="1" t="s">
-        <v>46</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet28.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{134F1CA8-51CC-4F47-A29E-A177BC4A1197}">
-  <dimension ref="A1:A2"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" outlineLevelRow="1"/>
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" t="s">
@@ -1518,75 +2131,81 @@
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <headerFooter/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet29.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A927210F-6B1B-4928-90B8-459FFB018D2A}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
   <dimension ref="A1:B2"/>
-  <sheetFormatPr defaultColWidth="12.7109375" defaultRowHeight="15"/>
+  <sheetFormatPr defaultColWidth="12.7083333333333" defaultRowHeight="14" outlineLevelRow="1" outlineLevelCol="1"/>
   <sheetData>
     <row r="1" spans="1:2">
-      <c r="A1" s="1" t="s">
+      <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="B1" s="2" t="s">
         <v>7</v>
       </c>
     </row>
     <row r="2" spans="1:2">
-      <c r="A2" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="B2" s="1" t="s">
+      <c r="A2" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="B2" s="2" t="s">
         <v>8</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <headerFooter/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F140B6DE-C2D2-4E53-B788-B28FEB24F709}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
   <dimension ref="A1:B3"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" outlineLevelRow="2" outlineLevelCol="1"/>
   <sheetData>
     <row r="1" spans="1:2">
-      <c r="A1" s="1" t="s">
+      <c r="A1" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="B1" s="2" t="s">
         <v>5</v>
       </c>
     </row>
     <row r="2" spans="1:2">
-      <c r="A2" s="1" t="s">
+      <c r="A2" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="B2" s="1" t="s">
+      <c r="B2" s="2" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="3" spans="1:2">
-      <c r="A3" s="1"/>
-      <c r="B3" s="1"/>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+      <c r="A3" s="2"/>
+      <c r="B3" s="2"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <headerFooter/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet30.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C20356A6-121F-4A5C-B576-D1B1F7F01AA7}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
   <dimension ref="A1:E2"/>
-  <sheetFormatPr defaultColWidth="18.7109375" defaultRowHeight="15"/>
+  <sheetFormatPr defaultColWidth="18.7083333333333" defaultRowHeight="14" outlineLevelRow="1" outlineLevelCol="4"/>
   <sheetData>
     <row r="1" spans="1:5">
-      <c r="A1" s="1" t="s">
+      <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="B1" s="2" t="s">
         <v>7</v>
       </c>
       <c r="C1" t="s">
@@ -1600,10 +2219,10 @@
       </c>
     </row>
     <row r="2" spans="1:5">
-      <c r="A2" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="B2" s="1" t="s">
+      <c r="A2" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="B2" s="2" t="s">
         <v>8</v>
       </c>
       <c r="C2" t="s">
@@ -1618,22 +2237,24 @@
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <headerFooter/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet31.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{82A38493-F7C2-4BEC-862C-A60806D7FBDC}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
   <dimension ref="A1:H2"/>
-  <sheetFormatPr defaultColWidth="18.42578125" defaultRowHeight="15"/>
+  <sheetFormatPr defaultColWidth="18.425" defaultRowHeight="14" outlineLevelRow="1" outlineLevelCol="7"/>
   <sheetData>
     <row r="1" spans="1:8">
-      <c r="A1" s="1" t="s">
+      <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="B1" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="C1" s="2" t="s">
         <v>55</v>
       </c>
       <c r="D1" t="s">
@@ -1653,25 +2274,25 @@
       </c>
     </row>
     <row r="2" spans="1:8">
-      <c r="A2" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="B2" s="1" t="s">
+      <c r="A2" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="B2" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="C2" s="1" t="s">
+      <c r="C2" s="2" t="s">
         <v>59</v>
       </c>
       <c r="D2" t="s">
         <v>60</v>
       </c>
-      <c r="E2" s="7">
+      <c r="E2" s="4">
         <v>45944</v>
       </c>
-      <c r="F2" s="7">
+      <c r="F2" s="4">
         <v>45996</v>
       </c>
-      <c r="G2" s="7" t="s">
+      <c r="G2" s="4" t="s">
         <v>61</v>
       </c>
       <c r="H2" t="s">
@@ -1680,151 +2301,161 @@
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <headerFooter/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet32.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6C05D563-E296-4E56-B274-3FD7933F43EB}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
   <dimension ref="A1:B2"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" outlineLevelRow="1" outlineLevelCol="1"/>
   <cols>
-    <col min="1" max="1" width="22.5703125" customWidth="1"/>
-    <col min="2" max="2" width="25.42578125" customWidth="1"/>
+    <col min="1" max="1" width="22.575" customWidth="1"/>
+    <col min="2" max="2" width="25.425" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:2">
-      <c r="A1" s="1" t="s">
+      <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="B1" s="2" t="s">
         <v>7</v>
       </c>
     </row>
     <row r="2" spans="1:2">
-      <c r="A2" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="B2" s="1" t="s">
+      <c r="A2" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="B2" s="2" t="s">
         <v>63</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <headerFooter/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet33.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BF91708B-AD91-4650-881E-5102D1C56010}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
   <dimension ref="A1:B2"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" outlineLevelRow="1" outlineLevelCol="1"/>
   <cols>
-    <col min="1" max="2" width="20.28515625" customWidth="1"/>
+    <col min="1" max="2" width="20.2833333333333" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:2">
-      <c r="A1" s="1" t="s">
+      <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="B1" s="2" t="s">
         <v>7</v>
       </c>
     </row>
     <row r="2" spans="1:2">
-      <c r="A2" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="B2" s="1" t="s">
+      <c r="A2" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="B2" s="2" t="s">
         <v>63</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <headerFooter/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet34.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{461D058D-6F7E-4A56-A8CC-74F4E08310C3}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
   <dimension ref="A1:C2"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" outlineLevelRow="1" outlineLevelCol="2"/>
   <sheetData>
     <row r="1" spans="1:3">
-      <c r="A1" s="1" t="s">
+      <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="B1" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="C1" s="2" t="s">
         <v>64</v>
       </c>
     </row>
     <row r="2" spans="1:3">
-      <c r="A2" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="B2" s="1" t="s">
+      <c r="A2" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="B2" s="2" t="s">
         <v>44</v>
       </c>
-      <c r="C2" s="1" t="s">
+      <c r="C2" s="2" t="s">
         <v>65</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <headerFooter/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet35.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7981D99A-26E1-481F-9B6E-1338C62D7C5E}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
   <dimension ref="A1:C2"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" outlineLevelRow="1" outlineLevelCol="2"/>
   <sheetData>
     <row r="1" spans="1:3">
-      <c r="A1" s="1" t="s">
+      <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="B1" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="C1" s="2" t="s">
         <v>64</v>
       </c>
     </row>
     <row r="2" spans="1:3">
-      <c r="A2" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="B2" s="1" t="s">
+      <c r="A2" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="B2" s="2" t="s">
         <v>44</v>
       </c>
-      <c r="C2" s="1" t="s">
+      <c r="C2" s="2" t="s">
         <v>65</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <headerFooter/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet36.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3C2361B9-9799-4DA5-A858-4C7D5F2938AD}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
   <dimension ref="A1:D2"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" outlineLevelRow="1" outlineLevelCol="3"/>
   <cols>
-    <col min="1" max="1" width="21.140625" customWidth="1"/>
-    <col min="2" max="2" width="24.7109375" customWidth="1"/>
-    <col min="3" max="3" width="20.42578125" customWidth="1"/>
-    <col min="4" max="4" width="19.140625" customWidth="1"/>
+    <col min="1" max="1" width="21.1333333333333" customWidth="1"/>
+    <col min="2" max="2" width="24.7083333333333" customWidth="1"/>
+    <col min="3" max="3" width="20.425" customWidth="1"/>
+    <col min="4" max="4" width="19.1333333333333" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:4">
-      <c r="A1" s="1" t="s">
+      <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="B1" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="C1" s="2" t="s">
         <v>55</v>
       </c>
       <c r="D1" t="s">
@@ -1832,13 +2463,13 @@
       </c>
     </row>
     <row r="2" spans="1:4">
-      <c r="A2" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="B2" s="1" t="s">
+      <c r="A2" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="B2" s="2" t="s">
         <v>66</v>
       </c>
-      <c r="C2" s="1" t="s">
+      <c r="C2" s="2" t="s">
         <v>59</v>
       </c>
       <c r="D2" t="s">
@@ -1847,214 +2478,230 @@
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <headerFooter/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet37.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C144CF31-8E42-49B8-9A2C-12BDDB72814D}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
   <dimension ref="A1:D2"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" outlineLevelRow="1" outlineLevelCol="3"/>
   <sheetData>
     <row r="1" spans="1:4">
-      <c r="A1" s="1" t="s">
+      <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="B1" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="C1" s="2" t="s">
         <v>55</v>
       </c>
-      <c r="D1" s="8" t="s">
+      <c r="D1" s="2" t="s">
         <v>51</v>
       </c>
     </row>
     <row r="2" spans="1:4">
-      <c r="A2" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="B2" s="1" t="s">
+      <c r="A2" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="B2" s="2" t="s">
         <v>66</v>
       </c>
-      <c r="C2" s="1" t="s">
+      <c r="C2" s="2" t="s">
         <v>59</v>
       </c>
-      <c r="D2" s="8" t="s">
+      <c r="D2" s="2" t="s">
         <v>62</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <headerFooter/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet38.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B1BCF5D2-9D9D-4B9F-9E04-C9A945304465}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
   <dimension ref="A1:A2"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" outlineLevelRow="1"/>
   <sheetData>
     <row r="1" spans="1:1">
-      <c r="A1" s="1" t="s">
+      <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
     </row>
     <row r="2" spans="1:1">
-      <c r="A2" s="1" t="s">
-        <v>2</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+      <c r="A2" s="2" t="s">
+        <v>2</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <headerFooter/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet39.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D9721A66-420B-4872-BA3F-ADEFA4188419}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
   <dimension ref="A1:B2"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" outlineLevelRow="1" outlineLevelCol="1"/>
   <sheetData>
     <row r="1" spans="1:2">
-      <c r="A1" s="1" t="s">
+      <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="B1" s="2" t="s">
         <v>7</v>
       </c>
     </row>
     <row r="2" spans="1:2">
-      <c r="A2" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="B2" s="1" t="s">
+      <c r="A2" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="B2" s="2" t="s">
         <v>67</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <headerFooter/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F80421D6-66FD-4069-93EC-B830B5E7FB36}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
   <dimension ref="A1:B2"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" outlineLevelRow="1" outlineLevelCol="1"/>
   <cols>
     <col min="2" max="2" width="29" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:2">
-      <c r="A1" s="1" t="s">
+      <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="B1" s="2" t="s">
         <v>7</v>
       </c>
     </row>
     <row r="2" spans="1:2">
-      <c r="A2" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="B2" s="1" t="s">
+      <c r="A2" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="B2" s="2" t="s">
         <v>8</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <headerFooter/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet40.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C3CB73C2-0290-4842-B801-D1C325E347B7}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
   <dimension ref="A1:B2"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" outlineLevelRow="1" outlineLevelCol="1"/>
   <sheetData>
     <row r="1" spans="1:2">
-      <c r="A1" s="1" t="s">
+      <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="B1" s="2" t="s">
         <v>68</v>
       </c>
     </row>
     <row r="2" spans="1:2">
-      <c r="A2" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="B2" s="1" t="s">
+      <c r="A2" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="B2" s="2" t="s">
         <v>54</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <headerFooter/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet41.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{535DF645-373D-497E-B5B0-411EDA32EB58}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
   <dimension ref="A1:B2"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" outlineLevelRow="1" outlineLevelCol="1"/>
   <sheetData>
     <row r="1" spans="1:2">
-      <c r="A1" s="1" t="s">
+      <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="B1" s="2" t="s">
         <v>55</v>
       </c>
     </row>
     <row r="2" spans="1:2">
-      <c r="A2" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="B2" s="1" t="s">
+      <c r="A2" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="B2" s="2" t="s">
         <v>62</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <headerFooter/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet42.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{02726931-E7D5-4380-B692-5DA16C8C288B}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
   <dimension ref="A1:B2"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" outlineLevelRow="1" outlineLevelCol="1"/>
   <sheetData>
     <row r="1" spans="1:2">
-      <c r="A1" s="1" t="s">
+      <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="B1" s="2" t="s">
         <v>4</v>
       </c>
     </row>
     <row r="2" spans="1:2">
-      <c r="A2" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="B2" s="1" t="s">
+      <c r="A2" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="B2" s="2" t="s">
         <v>69</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <headerFooter/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet43.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B1C35D31-E31B-4A53-820B-7AC9D195ADF5}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
   <dimension ref="A1:C2"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" outlineLevelRow="1" outlineLevelCol="2"/>
   <cols>
-    <col min="1" max="1" width="17.42578125" customWidth="1"/>
-    <col min="2" max="2" width="17.28515625" customWidth="1"/>
+    <col min="1" max="1" width="17.425" customWidth="1"/>
+    <col min="2" max="2" width="17.2833333333333" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3">
-      <c r="A1" s="1" t="s">
+      <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="B1" s="2" t="s">
         <v>4</v>
       </c>
       <c r="C1" t="s">
@@ -2062,10 +2709,10 @@
       </c>
     </row>
     <row r="2" spans="1:3">
-      <c r="A2" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="B2" s="1" t="s">
+      <c r="A2" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="B2" s="2" t="s">
         <v>69</v>
       </c>
       <c r="C2" t="s">
@@ -2074,119 +2721,127 @@
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <headerFooter/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet44.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EF350125-E0BA-4DE6-A057-A80A92798C47}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
   <dimension ref="A1:C2"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" outlineLevelRow="1" outlineLevelCol="2"/>
   <cols>
-    <col min="1" max="1" width="21.5703125" customWidth="1"/>
-    <col min="2" max="2" width="16.42578125" customWidth="1"/>
-    <col min="3" max="3" width="22.5703125" customWidth="1"/>
+    <col min="1" max="1" width="21.575" customWidth="1"/>
+    <col min="2" max="2" width="16.425" customWidth="1"/>
+    <col min="3" max="3" width="22.575" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3">
-      <c r="A1" s="1" t="s">
+      <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="B1" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="C1" s="8" t="s">
+      <c r="C1" s="2" t="s">
         <v>71</v>
       </c>
     </row>
     <row r="2" spans="1:3">
-      <c r="A2" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="B2" s="1" t="s">
+      <c r="A2" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="B2" s="2" t="s">
         <v>69</v>
       </c>
-      <c r="C2" s="8" t="s">
+      <c r="C2" s="2" t="s">
         <v>72</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <headerFooter/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet45.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FF50CBB7-83F3-4F98-974A-85C4D0E474C0}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
   <dimension ref="A1:C2"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" outlineLevelRow="1" outlineLevelCol="2"/>
   <cols>
-    <col min="1" max="1" width="24.85546875" customWidth="1"/>
-    <col min="2" max="2" width="29.28515625" customWidth="1"/>
-    <col min="3" max="3" width="22.42578125" customWidth="1"/>
+    <col min="1" max="1" width="24.8583333333333" customWidth="1"/>
+    <col min="2" max="2" width="29.2833333333333" customWidth="1"/>
+    <col min="3" max="3" width="22.425" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3">
-      <c r="A1" s="1" t="s">
+      <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="B1" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="C1" s="9" t="s">
+      <c r="C1" s="5" t="s">
         <v>73</v>
       </c>
     </row>
     <row r="2" spans="1:3">
-      <c r="A2" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="B2" s="1" t="s">
+      <c r="A2" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="B2" s="2" t="s">
         <v>69</v>
       </c>
-      <c r="C2" s="1" t="s">
+      <c r="C2" s="2" t="s">
         <v>74</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <headerFooter/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet46.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6E1A2B02-A6F3-4D1E-A8CD-6C31E80B3F37}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
   <dimension ref="A1:B2"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" outlineLevelRow="1" outlineLevelCol="1"/>
   <sheetData>
     <row r="1" spans="1:2">
-      <c r="A1" s="1" t="s">
+      <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="B1" s="2" t="s">
         <v>7</v>
       </c>
     </row>
     <row r="2" spans="1:2">
-      <c r="A2" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="B2" s="1" t="s">
+      <c r="A2" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="B2" s="2" t="s">
         <v>8</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <headerFooter/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet47.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{46C04CB7-6319-4A7D-8D43-3A1180326B13}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
   <dimension ref="A1:E2"/>
-  <sheetFormatPr defaultColWidth="17.140625" defaultRowHeight="15"/>
+  <sheetFormatPr defaultColWidth="17.1333333333333" defaultRowHeight="14" outlineLevelRow="1" outlineLevelCol="4"/>
   <sheetData>
     <row r="1" spans="1:5">
-      <c r="A1" s="1" t="s">
+      <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="B1" s="2" t="s">
         <v>7</v>
       </c>
       <c r="C1" t="s">
@@ -2200,10 +2855,10 @@
       </c>
     </row>
     <row r="2" spans="1:5">
-      <c r="A2" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="B2" s="1" t="s">
+      <c r="A2" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="B2" s="2" t="s">
         <v>8</v>
       </c>
       <c r="C2" t="s">
@@ -2218,22 +2873,24 @@
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <headerFooter/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet48.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{45905268-8B6C-4328-B08D-F43D3DC88105}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
   <dimension ref="A1:H2"/>
-  <sheetFormatPr defaultColWidth="15.85546875" defaultRowHeight="15"/>
+  <sheetFormatPr defaultColWidth="15.8583333333333" defaultRowHeight="14" outlineLevelRow="1" outlineLevelCol="7"/>
   <sheetData>
     <row r="1" spans="1:8">
-      <c r="A1" s="1" t="s">
+      <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="B1" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="C1" s="2" t="s">
         <v>55</v>
       </c>
       <c r="D1" t="s">
@@ -2253,25 +2910,25 @@
       </c>
     </row>
     <row r="2" spans="1:8">
-      <c r="A2" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="B2" s="1" t="s">
+      <c r="A2" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="B2" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="C2" s="1" t="s">
+      <c r="C2" s="2" t="s">
         <v>59</v>
       </c>
       <c r="D2" t="s">
         <v>60</v>
       </c>
-      <c r="E2" s="7">
+      <c r="E2" s="4">
         <v>45944</v>
       </c>
-      <c r="F2" s="7">
+      <c r="F2" s="4">
         <v>45996</v>
       </c>
-      <c r="G2" s="7" t="s">
+      <c r="G2" s="4" t="s">
         <v>61</v>
       </c>
       <c r="H2" t="s">
@@ -2280,367 +2937,391 @@
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <headerFooter/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet49.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E89A57D9-1230-41D4-A826-BA183F8989D7}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
   <dimension ref="A1:D2"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" outlineLevelRow="1" outlineLevelCol="3"/>
   <sheetData>
     <row r="1" spans="1:4">
-      <c r="A1" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="B1" s="1" t="s">
+      <c r="A1" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="B1" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="C1" s="2" t="s">
         <v>23</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="D1" s="2" t="s">
         <v>24</v>
       </c>
     </row>
     <row r="2" spans="1:4">
-      <c r="A2" s="1" t="s">
+      <c r="A2" s="2" t="s">
         <v>42</v>
       </c>
-      <c r="B2" s="1" t="s">
+      <c r="B2" s="2" t="s">
         <v>44</v>
       </c>
-      <c r="C2" s="1" t="s">
+      <c r="C2" s="2" t="s">
         <v>45</v>
       </c>
-      <c r="D2" s="1" t="s">
+      <c r="D2" s="2" t="s">
         <v>46</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <headerFooter/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F9A6FCBD-35C4-4C28-ACB8-2DC5BCF411C1}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
   <dimension ref="A1:B2"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" outlineLevelRow="1" outlineLevelCol="1"/>
   <cols>
     <col min="1" max="1" width="32" customWidth="1"/>
-    <col min="2" max="2" width="15.7109375" customWidth="1"/>
+    <col min="2" max="2" width="15.7083333333333" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:2">
-      <c r="A1" s="1" t="s">
+      <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="B1" s="2" t="s">
         <v>7</v>
       </c>
     </row>
     <row r="2" spans="1:2">
-      <c r="A2" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="B2" s="1" t="s">
+      <c r="A2" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="B2" s="2" t="s">
         <v>8</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <headerFooter/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet50.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6D7CB24C-5CA3-4930-9375-B3F255526E94}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
   <dimension ref="A1:C2"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" outlineLevelRow="1" outlineLevelCol="2"/>
   <sheetData>
     <row r="1" spans="1:3">
-      <c r="A1" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="B1" s="1" t="s">
+      <c r="A1" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="B1" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="C1" s="2" t="s">
         <v>23</v>
       </c>
     </row>
     <row r="2" spans="1:3">
-      <c r="A2" s="1" t="s">
+      <c r="A2" s="2" t="s">
         <v>42</v>
       </c>
-      <c r="B2" s="1" t="s">
+      <c r="B2" s="2" t="s">
         <v>44</v>
       </c>
-      <c r="C2" s="1" t="s">
+      <c r="C2" s="2" t="s">
         <v>29</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <headerFooter/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet51.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4C1FBD25-83A5-45B0-99A7-18F9C11F46EB}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
   <dimension ref="A1:B2"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" outlineLevelRow="1" outlineLevelCol="1"/>
   <sheetData>
     <row r="1" spans="1:2">
-      <c r="A1" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="B1" s="1" t="s">
+      <c r="A1" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="B1" s="2" t="s">
         <v>7</v>
       </c>
     </row>
     <row r="2" spans="1:2">
-      <c r="A2" s="1" t="s">
+      <c r="A2" s="2" t="s">
         <v>42</v>
       </c>
-      <c r="B2" s="1" t="s">
+      <c r="B2" s="2" t="s">
         <v>43</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <headerFooter/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet52.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8E6A0C1C-DC6D-4FD7-98C0-900200610B51}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
   <dimension ref="A1:C2"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" outlineLevelRow="1" outlineLevelCol="2"/>
   <sheetData>
     <row r="1" spans="1:3">
-      <c r="A1" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="B1" s="1" t="s">
+      <c r="A1" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="B1" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="C1" s="1"/>
+      <c r="C1" s="2"/>
     </row>
     <row r="2" spans="1:3">
-      <c r="A2" s="1" t="s">
+      <c r="A2" s="2" t="s">
         <v>42</v>
       </c>
-      <c r="B2" s="1" t="s">
+      <c r="B2" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="C2" s="1"/>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+      <c r="C2" s="2"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <headerFooter/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet53.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{104DB61E-4FB3-4F1C-96B6-4C37BC0D2F7A}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
   <dimension ref="A1:C2"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" outlineLevelRow="1" outlineLevelCol="2"/>
   <sheetData>
     <row r="1" spans="1:3">
-      <c r="A1" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="B1" s="1" t="s">
+      <c r="A1" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="B1" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="C1" s="1"/>
+      <c r="C1" s="2"/>
     </row>
     <row r="2" spans="1:3">
-      <c r="A2" s="1" t="s">
+      <c r="A2" s="2" t="s">
         <v>42</v>
       </c>
-      <c r="B2" s="1" t="s">
+      <c r="B2" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="C2" s="1"/>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+      <c r="C2" s="2"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <headerFooter/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet54.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DB281C57-1C4A-49BA-B158-D4DC335E1860}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
   <dimension ref="A1:B2"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" outlineLevelRow="1" outlineLevelCol="1"/>
   <sheetData>
     <row r="1" spans="1:2">
-      <c r="A1" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="B1" s="1" t="s">
+      <c r="A1" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="B1" s="2" t="s">
         <v>7</v>
       </c>
     </row>
     <row r="2" spans="1:2">
-      <c r="A2" s="1" t="s">
+      <c r="A2" s="2" t="s">
         <v>42</v>
       </c>
-      <c r="B2" s="1" t="s">
+      <c r="B2" s="2" t="s">
         <v>43</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <headerFooter/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet55.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FFD9DE16-BB6C-4976-A1D9-B371122E734F}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
   <dimension ref="A1:D2"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" outlineLevelRow="1" outlineLevelCol="3"/>
   <sheetData>
     <row r="1" spans="1:4">
-      <c r="A1" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="B1" s="1" t="s">
+      <c r="A1" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="B1" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="C1" s="2" t="s">
         <v>75</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="D1" s="2" t="s">
         <v>76</v>
       </c>
     </row>
     <row r="2" spans="1:4">
-      <c r="A2" s="1" t="s">
+      <c r="A2" s="2" t="s">
         <v>42</v>
       </c>
-      <c r="B2" s="1" t="s">
+      <c r="B2" s="2" t="s">
         <v>66</v>
       </c>
-      <c r="C2" s="1" t="s">
+      <c r="C2" s="2" t="s">
         <v>77</v>
       </c>
-      <c r="D2" s="1" t="s">
+      <c r="D2" s="2" t="s">
         <v>78</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <headerFooter/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet56.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{49665296-9ABB-42EA-8ABC-FADCC028E098}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
   <dimension ref="A1:C2"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" outlineLevelRow="1" outlineLevelCol="2"/>
   <sheetData>
     <row r="1" spans="1:3">
-      <c r="A1" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="B1" s="1" t="s">
+      <c r="A1" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="B1" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="C1" s="2" t="s">
         <v>75</v>
       </c>
     </row>
     <row r="2" spans="1:3">
-      <c r="A2" s="1" t="s">
+      <c r="A2" s="2" t="s">
         <v>42</v>
       </c>
-      <c r="B2" s="1" t="s">
+      <c r="B2" s="2" t="s">
         <v>66</v>
       </c>
-      <c r="C2" s="1" t="s">
+      <c r="C2" s="2" t="s">
         <v>79</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <headerFooter/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet57.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0096073F-CF56-483C-ADB8-B1FAC49C18F7}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
   <dimension ref="A1:D2"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" outlineLevelRow="1" outlineLevelCol="3"/>
   <sheetData>
     <row r="1" spans="1:4">
-      <c r="A1" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="B1" s="1" t="s">
+      <c r="A1" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="B1" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="C1" s="2" t="s">
         <v>75</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="D1" s="2" t="s">
         <v>76</v>
       </c>
     </row>
     <row r="2" spans="1:4">
-      <c r="A2" s="1" t="s">
+      <c r="A2" s="2" t="s">
         <v>42</v>
       </c>
-      <c r="B2" s="1" t="s">
+      <c r="B2" s="2" t="s">
         <v>66</v>
       </c>
-      <c r="C2" s="1" t="s">
+      <c r="C2" s="2" t="s">
         <v>77</v>
       </c>
-      <c r="D2" s="1" t="s">
+      <c r="D2" s="2" t="s">
         <v>78</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <headerFooter/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet58.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{71D15765-EB72-4911-A619-DAFF41F83B8C}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
   <dimension ref="A1:C2"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" outlineLevelRow="1" outlineLevelCol="2"/>
   <sheetData>
     <row r="1" spans="1:3">
-      <c r="A1" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="B1" s="1" t="s">
+      <c r="A1" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="B1" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="C1" s="2" t="s">
         <v>75</v>
       </c>
     </row>
     <row r="2" spans="1:3">
-      <c r="A2" s="1" t="s">
+      <c r="A2" s="2" t="s">
         <v>42</v>
       </c>
-      <c r="B2" s="1" t="s">
+      <c r="B2" s="2" t="s">
         <v>66</v>
       </c>
-      <c r="C2" s="1" t="s">
+      <c r="C2" s="2" t="s">
         <v>79</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <headerFooter/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet59.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0D50D711-D426-4770-BFAF-7FA229F7DC8F}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
   <dimension ref="A1:E2"/>
-  <sheetFormatPr defaultColWidth="15.7109375" defaultRowHeight="15"/>
+  <sheetFormatPr defaultColWidth="15.7083333333333" defaultRowHeight="14" outlineLevelRow="1" outlineLevelCol="4"/>
   <sheetData>
     <row r="1" spans="1:5">
-      <c r="A1" s="1" t="s">
+      <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="B1" s="2" t="s">
         <v>7</v>
       </c>
       <c r="C1" t="s">
@@ -2654,10 +3335,10 @@
       </c>
     </row>
     <row r="2" spans="1:5">
-      <c r="A2" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="B2" s="1" t="s">
+      <c r="A2" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="B2" s="2" t="s">
         <v>8</v>
       </c>
       <c r="C2" t="s">
@@ -2672,28 +3353,30 @@
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <headerFooter/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C98C1C57-C3BC-49E1-A13E-B0423DDBDD49}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
   <dimension ref="A1:B2"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" outlineLevelRow="1" outlineLevelCol="1"/>
   <cols>
-    <col min="1" max="1" width="30.42578125" customWidth="1"/>
+    <col min="1" max="1" width="30.425" customWidth="1"/>
     <col min="2" max="2" width="28" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:2">
-      <c r="A1" s="1" t="s">
+      <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="B1" s="2" t="s">
         <v>7</v>
       </c>
     </row>
     <row r="2" spans="1:2">
-      <c r="A2" s="1" t="s">
+      <c r="A2" s="2" t="s">
         <v>2</v>
       </c>
       <c r="B2" t="s">
@@ -2702,45 +3385,49 @@
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <headerFooter/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet60.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7E9559F3-627A-4F04-865B-9C24276170A9}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
   <dimension ref="A1:C2"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" outlineLevelRow="1" outlineLevelCol="2"/>
   <sheetData>
     <row r="1" spans="1:3">
-      <c r="A1" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="B1" s="1" t="s">
+      <c r="A1" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="B1" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="C1" s="2" t="s">
         <v>76</v>
       </c>
     </row>
     <row r="2" spans="1:3">
-      <c r="A2" s="1" t="s">
+      <c r="A2" s="2" t="s">
         <v>42</v>
       </c>
-      <c r="B2" s="1" t="s">
+      <c r="B2" s="2" t="s">
         <v>66</v>
       </c>
-      <c r="C2" s="1" t="s">
+      <c r="C2" s="2" t="s">
         <v>80</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <headerFooter/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet61.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{66AF110B-C3CC-4F7B-A5EF-FCAB71ADECA0}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
   <dimension ref="A1:C2"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" outlineLevelRow="1" outlineLevelCol="2"/>
   <sheetData>
     <row r="1" spans="1:3">
       <c r="A1" t="s">
@@ -2766,208 +3453,519 @@
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <headerFooter/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet62.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8A744D4C-BBD3-44A3-AD4F-5B5515EBB4FA}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
   <dimension ref="A1:B2"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" outlineLevelRow="1" outlineLevelCol="1"/>
+  <sheetData>
+    <row r="1" spans="1:2">
+      <c r="A1" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="B1" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2">
+      <c r="A2" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="B2" s="2" t="s">
+        <v>81</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <headerFooter/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet63.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
+  <dimension ref="A1:B2"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" outlineLevelRow="1" outlineLevelCol="1"/>
+  <sheetData>
+    <row r="1" spans="1:2">
+      <c r="A1" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="B1" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2">
+      <c r="A2" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="B2" s="2" t="s">
+        <v>81</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <headerFooter/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet64.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
+  <dimension ref="A1:B2"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" outlineLevelRow="1" outlineLevelCol="1"/>
+  <sheetData>
+    <row r="1" spans="1:2">
+      <c r="A1" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="B1" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2">
+      <c r="A2" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="B2" s="2" t="s">
+        <v>81</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <headerFooter/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet65.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
+  <dimension ref="A1:D2"/>
+  <sheetFormatPr defaultColWidth="20.2833333333333" defaultRowHeight="14" outlineLevelRow="1" outlineLevelCol="3"/>
+  <sheetData>
+    <row r="1" spans="1:4">
+      <c r="A1" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="B1" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="C1" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="D1" s="2" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4">
+      <c r="A2" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="B2" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="C2" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="D2" s="2" t="s">
+        <v>15</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <headerFooter/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet66.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
+  <dimension ref="A1:D2"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" outlineLevelRow="1" outlineLevelCol="3"/>
+  <sheetData>
+    <row r="1" spans="1:4">
+      <c r="A1" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="B1" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="C1" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="D1" s="2" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4">
+      <c r="A2" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="B2" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="C2" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="D2" s="2" t="s">
+        <v>15</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <headerFooter/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet67.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
+  <dimension ref="A1:H2"/>
+  <sheetFormatPr defaultColWidth="23.575" defaultRowHeight="14" outlineLevelRow="1" outlineLevelCol="7"/>
+  <sheetData>
+    <row r="1" spans="1:8">
+      <c r="A1" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="B1" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="C1" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="D1" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="E1" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="F1" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="G1" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="H1" s="2" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="2" spans="1:8">
+      <c r="A2" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="B2" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="C2" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="D2" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="E2" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="F2" s="3">
+        <v>45944</v>
+      </c>
+      <c r="G2" s="3">
+        <v>45955</v>
+      </c>
+      <c r="H2" s="2" t="s">
+        <v>21</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <headerFooter/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet68.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
+  <dimension ref="A1:D2"/>
+  <sheetFormatPr defaultColWidth="15.2833333333333" defaultRowHeight="14" outlineLevelRow="1" outlineLevelCol="3"/>
+  <sheetData>
+    <row r="1" spans="1:4">
+      <c r="A1" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4">
+      <c r="A2" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="C2" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="D2" s="1" t="s">
+        <v>27</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <headerFooter/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet69.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
+  <dimension ref="A1:C2"/>
+  <sheetFormatPr defaultColWidth="8.725" defaultRowHeight="14" outlineLevelRow="1" outlineLevelCol="2"/>
+  <cols>
+    <col min="1" max="1" width="18.275" customWidth="1"/>
+    <col min="2" max="2" width="19.6333333333333" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:3">
+      <c r="A1" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="B1" t="s">
+        <v>67</v>
+      </c>
+      <c r="C1" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3">
+      <c r="A2" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="B2" t="s">
+        <v>66</v>
+      </c>
+      <c r="C2" t="s">
+        <v>77</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <headerFooter/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
+  <dimension ref="A1:D2"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" outlineLevelRow="1" outlineLevelCol="3"/>
+  <cols>
+    <col min="1" max="1" width="33.7083333333333" customWidth="1"/>
+    <col min="2" max="2" width="25.8583333333333" customWidth="1"/>
+    <col min="3" max="3" width="26.8583333333333" customWidth="1"/>
+    <col min="4" max="4" width="43.575" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:4">
+      <c r="A1" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="B1" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="C1" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="D1" s="2" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4">
+      <c r="A2" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="B2" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="C2" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="D2" s="2" t="s">
+        <v>15</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <headerFooter/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet70.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
+  <dimension ref="A1:C2"/>
+  <sheetFormatPr defaultColWidth="8.725" defaultRowHeight="14" outlineLevelRow="1" outlineLevelCol="2"/>
+  <sheetData>
+    <row r="1" spans="1:3">
+      <c r="A1" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="B1" t="s">
+        <v>67</v>
+      </c>
+      <c r="C1" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3">
+      <c r="A2" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="B2" t="s">
+        <v>66</v>
+      </c>
+      <c r="C2" t="s">
+        <v>77</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <headerFooter/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet71.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
+  <dimension ref="A1:B2"/>
+  <sheetFormatPr defaultColWidth="8.66666666666667" defaultRowHeight="14" outlineLevelRow="1" outlineLevelCol="1"/>
   <sheetData>
     <row r="1" spans="1:2">
       <c r="A1" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="B1" s="1" t="s">
-        <v>7</v>
+      <c r="B1" t="s">
+        <v>67</v>
       </c>
     </row>
     <row r="2" spans="1:2">
       <c r="A2" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="B2" s="1" t="s">
-        <v>81</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet63.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{29C9ABBF-72B5-4B18-9C84-2CC23B2E8B70}">
-  <dimension ref="A1:B2"/>
-  <sheetFormatPr defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1" spans="1:2">
-      <c r="A1" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="2" spans="1:2">
-      <c r="A2" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="B2" s="1" t="s">
-        <v>81</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet64.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8E952BC8-4102-48A1-B461-D95AC6A7A86D}">
-  <dimension ref="A1:B2"/>
-  <sheetFormatPr defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1" spans="1:2">
-      <c r="A1" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="2" spans="1:2">
-      <c r="A2" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="B2" s="1" t="s">
-        <v>81</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet65.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{75FE5D48-B084-4EB0-990F-FF827953A86F}">
+        <v>2</v>
+      </c>
+      <c r="B2" t="s">
+        <v>66</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <headerFooter/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
   <dimension ref="A1:D2"/>
-  <sheetFormatPr defaultColWidth="20.28515625" defaultRowHeight="15"/>
+  <sheetFormatPr defaultColWidth="17.8583333333333" defaultRowHeight="14" outlineLevelRow="1" outlineLevelCol="3"/>
   <sheetData>
     <row r="1" spans="1:4">
-      <c r="A1" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="B1" s="1" t="s">
+      <c r="A1" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="B1" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="C1" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="D1" s="2" t="s">
         <v>12</v>
       </c>
     </row>
     <row r="2" spans="1:4">
-      <c r="A2" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="B2" s="1" t="s">
+      <c r="A2" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="B2" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="C2" s="1" t="s">
+      <c r="C2" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="D2" s="1" t="s">
+      <c r="D2" s="2" t="s">
         <v>15</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet66.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B86DA6A5-0C5F-444B-82B0-73B61076CAAF}">
-  <dimension ref="A1:D2"/>
-  <sheetFormatPr defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1" spans="1:4">
-      <c r="A1" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="B1" s="1" t="s">
+  <headerFooter/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
+  <dimension ref="A1:H2"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" outlineLevelRow="1" outlineLevelCol="7"/>
+  <cols>
+    <col min="1" max="1" width="36.1333333333333" customWidth="1"/>
+    <col min="2" max="2" width="25.425" customWidth="1"/>
+    <col min="3" max="3" width="25" customWidth="1"/>
+    <col min="4" max="4" width="24" customWidth="1"/>
+    <col min="5" max="5" width="31.2833333333333" customWidth="1"/>
+    <col min="6" max="6" width="13" customWidth="1"/>
+    <col min="7" max="7" width="17.2833333333333" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:8">
+      <c r="A1" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="B1" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="C1" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="D1" s="2" t="s">
         <v>12</v>
       </c>
-    </row>
-    <row r="2" spans="1:4">
-      <c r="A2" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="B2" s="1" t="s">
+      <c r="E1" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="F1" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="G1" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="H1" s="2" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="2" spans="1:8">
+      <c r="A2" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="B2" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="C2" s="1" t="s">
+      <c r="C2" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="D2" s="1" t="s">
+      <c r="D2" s="2" t="s">
         <v>15</v>
       </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet67.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{96602922-DDCA-4D06-9081-BBBF0D21A24D}">
-  <dimension ref="A1:H2"/>
-  <sheetFormatPr defaultColWidth="23.5703125" defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1" spans="1:8">
-      <c r="A1" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="F1" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="G1" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="H1" s="1" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="2" spans="1:8">
-      <c r="A2" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="B2" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="C2" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="D2" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="E2" s="1" t="s">
+      <c r="E2" s="2" t="s">
         <v>20</v>
       </c>
       <c r="F2" s="3">
@@ -2976,202 +3974,12 @@
       <c r="G2" s="3">
         <v>45955</v>
       </c>
-      <c r="H2" s="1" t="s">
+      <c r="H2" s="2" t="s">
         <v>21</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet68.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7D56171B-C60A-4894-836A-F56E7CF898EE}">
-  <dimension ref="A1:D2"/>
-  <sheetFormatPr defaultColWidth="15.28515625" defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1" spans="1:4">
-      <c r="A1" s="4" t="s">
-        <v>9</v>
-      </c>
-      <c r="B1" s="4" t="s">
-        <v>22</v>
-      </c>
-      <c r="C1" s="4" t="s">
-        <v>23</v>
-      </c>
-      <c r="D1" s="4" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="2" spans="1:4">
-      <c r="A2" s="4" t="s">
-        <v>2</v>
-      </c>
-      <c r="B2" s="4" t="s">
-        <v>25</v>
-      </c>
-      <c r="C2" s="4" t="s">
-        <v>26</v>
-      </c>
-      <c r="D2" s="4" t="s">
-        <v>27</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4CB98D22-48B2-48B5-888D-BA794D8ED98C}">
-  <dimension ref="A1:D2"/>
-  <sheetFormatPr defaultRowHeight="15"/>
-  <cols>
-    <col min="1" max="1" width="33.7109375" customWidth="1"/>
-    <col min="2" max="2" width="25.85546875" customWidth="1"/>
-    <col min="3" max="3" width="26.85546875" customWidth="1"/>
-    <col min="4" max="4" width="43.5703125" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:4">
-      <c r="A1" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="2" spans="1:4">
-      <c r="A2" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="B2" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="C2" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="D2" s="1" t="s">
-        <v>15</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{72E1AA3C-1966-498B-B131-F079F075CAC1}">
-  <dimension ref="A1:D2"/>
-  <sheetFormatPr defaultColWidth="17.85546875" defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1" spans="1:4">
-      <c r="A1" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="2" spans="1:4">
-      <c r="A2" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="B2" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="C2" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="D2" s="1" t="s">
-        <v>15</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{39A7D9B6-4BEA-4F32-A9AB-34D1DFFD8F2E}">
-  <dimension ref="A1:H2"/>
-  <sheetFormatPr defaultRowHeight="15"/>
-  <cols>
-    <col min="1" max="1" width="36.140625" customWidth="1"/>
-    <col min="2" max="2" width="25.42578125" customWidth="1"/>
-    <col min="3" max="3" width="25" customWidth="1"/>
-    <col min="4" max="4" width="24" customWidth="1"/>
-    <col min="5" max="5" width="31.28515625" customWidth="1"/>
-    <col min="6" max="6" width="13" customWidth="1"/>
-    <col min="7" max="7" width="17.28515625" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:8">
-      <c r="A1" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="F1" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="G1" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="H1" s="1" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="2" spans="1:8">
-      <c r="A2" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="B2" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="C2" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="D2" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="E2" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="F2" s="3">
-        <v>45944</v>
-      </c>
-      <c r="G2" s="3">
-        <v>45955</v>
-      </c>
-      <c r="H2" s="1" t="s">
-        <v>21</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <headerFooter/>
 </worksheet>
 </file>